--- a/data/input_file.xlsx
+++ b/data/input_file.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aelh\OneDrive - ALAN ALLMAN ASSOCIATES\Bureau\Git\linkedin-link-finder\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aelh\OneDrive - ALAN ALLMAN ASSOCIATES\Bureau\Git\linkedin_finder_exe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3BE0C7-DB00-4E38-93B2-652E7199D32D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20B4478-77DB-457C-8484-351D9EAB7468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="710" windowWidth="19230" windowHeight="10090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="532">
   <si>
     <t>Nom</t>
   </si>
@@ -1452,13 +1452,187 @@
     <t>https://fr.linkedin.com/in/nathalie-retter-350648111</t>
   </si>
   <si>
-    <t>Abdelmajid EL HOU</t>
-  </si>
-  <si>
-    <t>Data Engineer &amp; Scientist</t>
-  </si>
-  <si>
-    <t>Siderlog Conseil</t>
+    <t>Régalien risques &amp; finances</t>
+  </si>
+  <si>
+    <t>PLATEFORME FICE &amp; RISQUES - FICE &amp; REPORTING REGALIEN</t>
+  </si>
+  <si>
+    <t>Pilotage Synthèse &amp; Data</t>
+  </si>
+  <si>
+    <t>PLATEFORME SEF - DSI FACTOR</t>
+  </si>
+  <si>
+    <t>Achats Directeur</t>
+  </si>
+  <si>
+    <t>POLE FICE &amp; PILOTAGE</t>
+  </si>
+  <si>
+    <t>Chèques &amp; prélèvements</t>
+  </si>
+  <si>
+    <t>PLATEFORME SERVICES BANCAIRES - PAIEMENT - SERVICES B2C - B2B</t>
+  </si>
+  <si>
+    <t>Directeur</t>
+  </si>
+  <si>
+    <t>PLATEFORME ESPACE CLIENT, DATA &amp; IA</t>
+  </si>
+  <si>
+    <t>Directeur Adjoint</t>
+  </si>
+  <si>
+    <t>Responsable</t>
+  </si>
+  <si>
+    <t>PLATEFORME ESPACE CLIENT, DATA &amp; IA - ESPACE CLIENT</t>
+  </si>
+  <si>
+    <t>Responsable Adjoint</t>
+  </si>
+  <si>
+    <t>Ma banque en ligne web</t>
+  </si>
+  <si>
+    <t>Ma banque en ligne mobile</t>
+  </si>
+  <si>
+    <t>Portail</t>
+  </si>
+  <si>
+    <t>Banque en ligne B2C</t>
+  </si>
+  <si>
+    <t>Banque en ligne B2B</t>
+  </si>
+  <si>
+    <t>Banque en ligne mobile</t>
+  </si>
+  <si>
+    <t>PLATEFORME ESPACE CLIENT, DATA &amp; IA - ESPACE DE VENTE &amp; SOCLES</t>
+  </si>
+  <si>
+    <t>Sécurité digitale</t>
+  </si>
+  <si>
+    <t>Prospect &amp; Collecte</t>
+  </si>
+  <si>
+    <t>Budget - Compte</t>
+  </si>
+  <si>
+    <t>Portail &amp; souscriptions digitales</t>
+  </si>
+  <si>
+    <t>Socle &amp; données client</t>
+  </si>
+  <si>
+    <t>Identification &amp; services</t>
+  </si>
+  <si>
+    <t>PLATEFORME ESPACE CLIENT, DATA &amp; IA - USAGES DATA</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Pilote &amp; Analyse</t>
+  </si>
+  <si>
+    <t>PLATEFORME ESPACE CLIENT, DATA &amp; IA - SOCLES &amp; SOLUTIONS DATA</t>
+  </si>
+  <si>
+    <t>BARATIER LUCIE</t>
+  </si>
+  <si>
+    <t>LAFAURIE NICOLAS</t>
+  </si>
+  <si>
+    <t>RUDLOFF CORINNE</t>
+  </si>
+  <si>
+    <t>SARRAZIN OLIVIER</t>
+  </si>
+  <si>
+    <t>DURAND PIERRE-EMMANUEL</t>
+  </si>
+  <si>
+    <t>AMATO JEAN-FRANÇOIS</t>
+  </si>
+  <si>
+    <t>FRICOTTEAU ANAUD</t>
+  </si>
+  <si>
+    <t>BEAUCOURT YANNICK</t>
+  </si>
+  <si>
+    <t>MARTIN TOMY</t>
+  </si>
+  <si>
+    <t>DELBART VINCENT</t>
+  </si>
+  <si>
+    <t>DOUCET NICOLAS</t>
+  </si>
+  <si>
+    <t>MONCLA VÉRONIQUE</t>
+  </si>
+  <si>
+    <t>LOUKIL AMINE</t>
+  </si>
+  <si>
+    <t>CAPIGA GUILLAUME</t>
+  </si>
+  <si>
+    <t>LECOMTE SANDRINE</t>
+  </si>
+  <si>
+    <t>COUDERC ALAIN</t>
+  </si>
+  <si>
+    <t>KETIR NORA</t>
+  </si>
+  <si>
+    <t>FESQUET LAURENT</t>
+  </si>
+  <si>
+    <t>COSTE BENOIT</t>
+  </si>
+  <si>
+    <t>BASSET ARNAUD</t>
+  </si>
+  <si>
+    <t>BRUGNAUT DELPHINE</t>
+  </si>
+  <si>
+    <t>GAUDIN ARNAUD</t>
+  </si>
+  <si>
+    <t>MOLLAT MATHIEU</t>
+  </si>
+  <si>
+    <t>REPESSE STÉPHANE</t>
+  </si>
+  <si>
+    <t>GILBERT AURÉLIE</t>
+  </si>
+  <si>
+    <t>QUEULAIN JEAN-LUC</t>
+  </si>
+  <si>
+    <t>PITHON SÉBASTIEN</t>
+  </si>
+  <si>
+    <t>BOYER ASTRID</t>
+  </si>
+  <si>
+    <t>CORNATON SAFIA</t>
+  </si>
+  <si>
+    <t>CASTEX ARNAULD</t>
   </si>
 </sst>
 </file>
@@ -1889,131 +2063,423 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="C2" s="3"/>
       <c r="D2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>503</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
+      <c r="C3" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="D3" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
+      <c r="A4" t="s">
+        <v>504</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="D4" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
+      <c r="A5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D5" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
+      <c r="A6" t="s">
+        <v>506</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="D6" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
+      <c r="A7" t="s">
+        <v>507</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="D7" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
+      <c r="A8" t="s">
+        <v>508</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="D8" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
+      <c r="A9" t="s">
+        <v>509</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="D9" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
+      <c r="A10" t="s">
+        <v>510</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="D10" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
+      <c r="A11" t="s">
+        <v>511</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="D11" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
+      <c r="A12" t="s">
+        <v>512</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="D12" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
+      <c r="A13" t="s">
+        <v>513</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="D13" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
+      <c r="A14" t="s">
+        <v>514</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="D14" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
+      <c r="A15" t="s">
+        <v>515</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="D15" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
+      <c r="A16" t="s">
+        <v>516</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="D16" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>517</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="D17" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>518</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="D18" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>519</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="D19" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>520</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="D20" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>521</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="D21" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>522</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="D22" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>523</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="D23" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>524</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="D24" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>525</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="D25" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>526</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="D26" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>527</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="D27" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>528</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="D28" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>529</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="D29" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>530</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="D30" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>531</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="D31" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B73" s="2"/>
